--- a/data/trans_bre/IP18A05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,0</t>
+          <t>-2,29; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,75</t>
+          <t>-2,78; 0,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 10,44</t>
+          <t>-4,36; 10,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,48</t>
+          <t>-1,77; 0,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,81</t>
+          <t>-2,65; 0,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,02</t>
+          <t>-0,86; 3,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 8,55</t>
+          <t>-6,87; 8,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 160,69</t>
+          <t>-100,0; 189,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,37; 978,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,06</t>
+          <t>-1,78; 2,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,92</t>
+          <t>-1,12; 4,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,93</t>
+          <t>-0,48; 2,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 4,92</t>
+          <t>-12,95; 5,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,63</t>
+          <t>-1,4; 1,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,0</t>
+          <t>-2,8; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -0,73</t>
+          <t>-6,73; -0,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 4,07</t>
+          <t>-14,84; 4,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 155,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,85</t>
+          <t>-0,72; 0,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,55</t>
+          <t>-1,1; 0,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,87</t>
+          <t>-1,32; 0,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 2,44</t>
+          <t>-6,24; 2,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 389,36</t>
+          <t>-81,27; 358,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-73,59; 98,6</t>
+          <t>-73,8; 82,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-65,93; 126,33</t>
+          <t>-67,66; 105,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-89,06; 125,86</t>
+          <t>-90,42; 142,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,0</t>
+          <t>-2,32; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,63</t>
+          <t>-3,27; 0,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 10,23</t>
+          <t>-4,67; 9,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,26</t>
+          <t>-1,55; 0,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,97</t>
+          <t>-2,67; 0,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,22</t>
+          <t>-0,78; 3,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 8,55</t>
+          <t>-6,3; 8,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 189,9</t>
+          <t>-100,0; 156,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,23; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,92</t>
+          <t>-1,78; 2,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,22</t>
+          <t>-1,11; 4,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,87</t>
+          <t>-0,43; 2,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 5,1</t>
+          <t>-13,63; 4,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,65</t>
+          <t>-1,52; 1,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,0</t>
+          <t>-2,82; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -0,51</t>
+          <t>-6,9; -0,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 4,14</t>
+          <t>-14,57; 3,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 155,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,85</t>
+          <t>-0,63; 0,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,54</t>
+          <t>-1,17; 0,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,81</t>
+          <t>-1,31; 0,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 2,35</t>
+          <t>-6,08; 2,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 358,44</t>
+          <t>-80,02; 384,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-73,8; 82,69</t>
+          <t>-75,97; 103,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-67,66; 105,86</t>
+          <t>-68,33; 82,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-90,42; 142,83</t>
+          <t>-85,87; 135,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,0</t>
+          <t>-2,96; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,61</t>
+          <t>-2,91; 0,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 9,33</t>
+          <t>-3,96; 9,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,45</t>
+          <t>-1,77; 0,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,75</t>
+          <t>-2,54; 0,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,2</t>
+          <t>-0,85; 3,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 8,52</t>
+          <t>-7,46; 8,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 156,0</t>
+          <t>-100,0; 160,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,23; —</t>
+          <t>-90,37; 978,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-2,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-51,66%</t>
+          <t>-45,9%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,93</t>
+          <t>-1,79; 3,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 4,02</t>
+          <t>-1,04; 3,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,9</t>
+          <t>-0,47; 2,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 4,91</t>
+          <t>-12,39; 6,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-3,32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-55,13%</t>
+          <t>-63,87%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,37</t>
+          <t>-1,42; 1,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,0</t>
+          <t>-2,52; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -0,69</t>
+          <t>-6,84; -0,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 3,57</t>
+          <t>-16,79; 2,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-33,54%</t>
+          <t>-36,59%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,81</t>
+          <t>-0,66; 0,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,59</t>
+          <t>-1,15; 0,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,66</t>
+          <t>-1,32; 0,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 2,5</t>
+          <t>-7,05; 2,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-80,02; 384,51</t>
+          <t>-76,8; 389,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-75,97; 103,53</t>
+          <t>-73,59; 98,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-68,33; 82,77</t>
+          <t>-65,93; 126,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-85,87; 135,36</t>
+          <t>-90,42; 127,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,177 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-60,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22,44%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.6988603770678493</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.4580205645199614</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.6632553591999731</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.436171478499103</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.6076933163242152</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.2244056380146071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,82</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,96; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,91; 0,75</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,96; 9,83</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.957733715539685</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.91127933166994</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.958688402853018</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.817759066598518</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7483788666505636</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.830832114100426</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-56,53%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-45,88%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,77; 0,48</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,54; 0,81</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,85; 3,02</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-7,46; 8,5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 160,69</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-90,37; 978,05</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.3355861842334025</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.7939864970934832</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9330718758730089</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.2140044738009411</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.5653467922644697</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4588042874978172</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.9648717688197106</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.05479807748007985</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,03</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,47</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>131,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>243,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-45,9%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.77410148033891</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.537823035882004</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.8506950324181414</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-7.463093947357846</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.9037178870789085</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,79; 3,06</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,04; 3,92</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 2,93</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-12,39; 6,06</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.480830767286851</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.8064509054618323</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.020774716073212</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>8.501049687227887</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>1.606940902978006</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>9.780470073500735</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +797,265 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,82</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,06</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-21,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-85,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-63,87%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.6145957503889861</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.345198065119146</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.027088076279002</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.467589270258372</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.7395713438048198</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.318419418413083</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>2.430513235612267</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.4589536334076864</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,42; 1,63</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,52; 0,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,84; -0,73</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-16,79; 2,64</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.787338301784651</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.04413608464701</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.465742101828236</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-12.38927785324118</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.058132745438233</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.924183766920188</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.926096358913737</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.055994202431696</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.1543751657516655</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.8214252600953418</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-3.060169578004125</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-3.318310882234079</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2191866397617987</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.8575086424808716</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.6386954772966666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.415936407974057</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.523604799324096</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.838730397497285</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-16.79320322426795</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.628122916424687</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-0.7291574500259654</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.639873632218486</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-24,12%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-18,5%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-36,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 0,85</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,15; 0,55</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,32; 0,87</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-7,05; 2,41</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-76,8; 389,36</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-73,59; 98,6</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-65,93; 126,33</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-90,42; 127,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.05519143296536495</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.2687236737178609</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.2630966996693263</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.657317290887217</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.09771030796655124</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.2411762847566024</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1849929003580277</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.3659091201664524</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.6613498180508183</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.148829314535509</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.317886393158057</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-7.051049880257816</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7680477337247315</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.7359289459559678</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6593208707567378</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.9041606243637619</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.8533842969357939</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5471221944555321</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.8732050977106874</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.413484040426134</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>3.893583245054383</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.9860010258533942</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.263341045380128</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.272075345212049</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1063,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
